--- a/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513266_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513266_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5021</v>
+        <v>7.85</v>
       </c>
       <c r="E2" t="n">
-        <v>9.1846</v>
+        <v>7.0225</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3175</v>
+        <v>0.8275</v>
       </c>
       <c r="G2" t="n">
         <v>4.2794</v>
@@ -610,13 +610,13 @@
         <v>1.7622</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4474</v>
+        <v>1.7954</v>
       </c>
       <c r="T2" t="n">
-        <v>3.7257</v>
+        <v>1.5636</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7217</v>
+        <v>0.2317</v>
       </c>
       <c r="V2" t="n">
         <v>1.1144</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6132</v>
+        <v>-0.6682</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.208</v>
+        <v>-0.3783</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4052</v>
+        <v>-0.2899</v>
       </c>
       <c r="G3" t="n">
         <v>-2.132</v>
@@ -688,13 +688,13 @@
         <v>1.1014</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4174</v>
+        <v>0.3624</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4889</v>
+        <v>0.3186</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.07149999999999999</v>
+        <v>0.0438</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.9277</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2543</v>
+        <v>0.9669</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.154</v>
+        <v>-1.8946</v>
       </c>
       <c r="G4" t="n">
         <v>-0.921</v>
@@ -766,13 +766,13 @@
         <v>2.6433</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6821</v>
+        <v>0.6541</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1262</v>
+        <v>0.8388</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4441</v>
+        <v>-0.1846</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2984</v>
+        <v>-0.9487</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1069</v>
+        <v>2.3412</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.4052</v>
+        <v>-3.2899</v>
       </c>
       <c r="G5" t="n">
         <v>-1.502</v>
@@ -844,13 +844,13 @@
         <v>1.1014</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.1781</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2922</v>
+        <v>-0.0578</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2356</v>
+        <v>-0.1203</v>
       </c>
       <c r="V5" t="n">
         <v>-0.37</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7946</v>
+        <v>-1.3521</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4822</v>
+        <v>0.7806</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2768</v>
+        <v>-2.1327</v>
       </c>
       <c r="G6" t="n">
         <v>0.2093</v>
@@ -922,13 +922,13 @@
         <v>1.1014</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.885</v>
+        <v>-0.4425</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4203</v>
+        <v>-0.1219</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4647</v>
+        <v>-0.3206</v>
       </c>
       <c r="V6" t="n">
         <v>-1.1189</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.1936</v>
+        <v>-3.6646</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8868</v>
+        <v>-2.5885</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3068</v>
+        <v>-1.0762</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0903</v>
@@ -1000,13 +1000,13 @@
         <v>1.1014</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0195</v>
+        <v>-0.4905</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.3141</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4071</v>
+        <v>-0.1765</v>
       </c>
       <c r="V7" t="n">
         <v>1.1189</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.4353</v>
+        <v>-3.7305</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4871</v>
+        <v>-1.667</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9482</v>
+        <v>-2.0635</v>
       </c>
       <c r="G8" t="n">
         <v>-4.3016</v>
@@ -1078,13 +1078,13 @@
         <v>2.423</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.169</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0405</v>
+        <v>0.8607</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2096</v>
+        <v>-0.3249</v>
       </c>
       <c r="V8" t="n">
         <v>-0.185</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.1117</v>
+        <v>-6.2232</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3221</v>
+        <v>-3.0878</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7895</v>
+        <v>-3.1354</v>
       </c>
       <c r="G9" t="n">
         <v>-8.5131</v>
@@ -1156,13 +1156,13 @@
         <v>2.2027</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3662</v>
+        <v>0.2546</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3451</v>
+        <v>0.5794</v>
       </c>
       <c r="U9" t="n">
-        <v>0.021</v>
+        <v>-0.3249</v>
       </c>
       <c r="V9" t="n">
         <v>0.9339</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.1852</v>
+        <v>-7.0443</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.3551</v>
+        <v>-6.3007</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8300999999999999</v>
+        <v>-0.7436</v>
       </c>
       <c r="G10" t="n">
         <v>-4.1139</v>
@@ -1234,13 +1234,13 @@
         <v>1.9825</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.547</v>
+        <v>0.594</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3719</v>
+        <v>0.6826</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.175</v>
+        <v>-0.0886</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-17.0296</v>
+        <v>-16.7093</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2311</v>
+        <v>-2.911100000000001</v>
       </c>
       <c r="F11" t="n">
         <v>-13.7983</v>
@@ -1312,10 +1312,10 @@
         <v>15.4193</v>
       </c>
       <c r="S11" t="n">
-        <v>2.764899999999999</v>
+        <v>3.0852</v>
       </c>
       <c r="T11" t="n">
-        <v>4.0296</v>
+        <v>4.349900000000001</v>
       </c>
       <c r="U11" t="n">
         <v>-1.2649</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.1986</v>
+        <v>5.1713</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9548</v>
+        <v>2.5406</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2438</v>
+        <v>2.6307</v>
       </c>
       <c r="G12" t="n">
         <v>2.6514</v>
@@ -1390,13 +1390,13 @@
         <v>3.0838</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5365</v>
+        <v>-0.5639</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5203</v>
+        <v>0.0655</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0163</v>
+        <v>-0.6294</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4718</v>
+        <v>4.3924</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9831</v>
+        <v>3.9515</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5113</v>
+        <v>0.4409</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6355</v>
+        <v>3.276</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0346</v>
+        <v>-1.771</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6701</v>
+        <v>5.047</v>
       </c>
       <c r="J13" t="n">
-        <v>4.119</v>
+        <v>3.8153</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9346</v>
+        <v>-0.34</v>
       </c>
       <c r="L13" t="n">
-        <v>3.1844</v>
+        <v>4.1554</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4835</v>
+        <v>-0.5394</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9692</v>
+        <v>-1.431</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5143</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8811</v>
+        <v>2.2027</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8811</v>
+        <v>3.3041</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0448</v>
+        <v>-0.5268</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.136</v>
+        <v>0.1186</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0911</v>
+        <v>-0.6455</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.5595</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1189</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.6784</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. LOBACO MUNOZ</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3523</v>
+        <v>3.6178</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4025</v>
+        <v>4.1002</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9498</v>
+        <v>-0.4825</v>
       </c>
       <c r="G14" t="n">
-        <v>3.867</v>
+        <v>2.6355</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3479</v>
+        <v>-0.0346</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5192</v>
+        <v>2.6701</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9378</v>
+        <v>4.119</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3102</v>
+        <v>0.9346</v>
       </c>
       <c r="L14" t="n">
-        <v>1.6275</v>
+        <v>3.1844</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0707</v>
+        <v>-1.4835</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9624</v>
+        <v>-0.9692</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8915999999999999</v>
+        <v>-0.5143</v>
       </c>
       <c r="P14" t="n">
         <v>0.8811</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.0838</v>
+        <v>0.8811</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0975</v>
+        <v>0.1011</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0419</v>
+        <v>-0.0188</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9444</v>
+        <v>0.1199</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.4934</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3745</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.1189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>R. LOBACO MUNOZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2738</v>
+        <v>2.9822</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2486</v>
+        <v>1.9338</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0252</v>
+        <v>1.0484</v>
       </c>
       <c r="G15" t="n">
-        <v>3.276</v>
+        <v>3.867</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.771</v>
+        <v>1.3479</v>
       </c>
       <c r="I15" t="n">
-        <v>5.047</v>
+        <v>2.5192</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8153</v>
+        <v>3.9378</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.34</v>
+        <v>2.3102</v>
       </c>
       <c r="L15" t="n">
-        <v>4.1554</v>
+        <v>1.6275</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5394</v>
+        <v>-0.0707</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.431</v>
+        <v>-0.9624</v>
       </c>
       <c r="O15" t="n">
         <v>0.8915999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2027</v>
+        <v>0.8811</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1014</v>
+        <v>-2.2027</v>
       </c>
       <c r="R15" t="n">
-        <v>3.3041</v>
+        <v>3.0838</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6454</v>
+        <v>-0.2726</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5843</v>
+        <v>0.5732</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0611</v>
+        <v>-0.8458</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5595</v>
+        <v>-1.4934</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1189</v>
+        <v>-0.3745</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6784</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0841</v>
+        <v>2.4226</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8446</v>
+        <v>2.4305</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2395</v>
+        <v>-0.0078</v>
       </c>
       <c r="G16" t="n">
         <v>5.507</v>
@@ -1702,13 +1702,13 @@
         <v>3.3041</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6782</v>
+        <v>-0.3397</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4562</v>
+        <v>0.1296</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.222</v>
+        <v>-0.4693</v>
       </c>
       <c r="V16" t="n">
         <v>0.5595</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0471</v>
+        <v>1.5208</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4141</v>
+        <v>2.9455</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.367</v>
+        <v>-1.4247</v>
       </c>
       <c r="G17" t="n">
         <v>1.0411</v>
@@ -1780,13 +1780,13 @@
         <v>1.3216</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1306</v>
+        <v>-0.6569</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5249</v>
+        <v>0.0562</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6555</v>
+        <v>-0.7131</v>
       </c>
       <c r="V17" t="n">
         <v>-0.185</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5292</v>
+        <v>0.3628</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3505</v>
+        <v>-0.702</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8797</v>
+        <v>1.0647</v>
       </c>
       <c r="G19" t="n">
         <v>0.51</v>
@@ -1936,13 +1936,13 @@
         <v>1.7622</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4598</v>
+        <v>0.2933</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6732</v>
+        <v>0.3217</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2135</v>
+        <v>-0.0284</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5493</v>
+        <v>-0.6916</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3249</v>
+        <v>-1.2078</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7756</v>
+        <v>0.5162</v>
       </c>
       <c r="G20" t="n">
         <v>1.0923</v>
@@ -2014,13 +2014,13 @@
         <v>0.2203</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0292</v>
+        <v>-0.1714</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4203</v>
+        <v>-0.3031</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3911</v>
+        <v>0.1317</v>
       </c>
       <c r="V20" t="n">
         <v>0.37</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9476</v>
+        <v>-2.5371</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9434</v>
+        <v>-2.7636</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0042</v>
+        <v>0.2264</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0647</v>
@@ -2092,13 +2092,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7427</v>
+        <v>0.1531</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1419</v>
+        <v>0.3217</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3992</v>
+        <v>-0.1686</v>
       </c>
       <c r="V21" t="n">
         <v>-0.185</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>17.0296</v>
+        <v>17.8108</v>
       </c>
       <c r="E22" t="n">
-        <v>13.7985</v>
+        <v>13.7983</v>
       </c>
       <c r="F22" t="n">
-        <v>3.2311</v>
+        <v>4.012300000000001</v>
       </c>
       <c r="G22" t="n">
         <v>19.0852</v>
@@ -2170,13 +2170,13 @@
         <v>17.6218</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.7647</v>
+        <v>-1.9838</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2648</v>
+        <v>1.2646</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.0298</v>
+        <v>-3.2485</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4934</v>
